--- a/exports/trend_1d/BSE_full_report.xlsx
+++ b/exports/trend_1d/BSE_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q60"/>
+  <dimension ref="A1:U60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>11.24</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42956</v>
+        <v>42957</v>
       </c>
       <c r="H2" t="n">
-        <v>116.5</v>
+        <v>112.5</v>
       </c>
       <c r="I2" t="n">
         <v>115.2919589604424</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="K2" t="n">
-        <v>8.369999999999999</v>
+        <v>4.65</v>
       </c>
       <c r="L2" t="n">
         <v>8.369999999999999</v>
@@ -555,7 +578,7 @@
         <v>0.86</v>
       </c>
       <c r="N2" t="n">
-        <v>2.94</v>
+        <v>3.43</v>
       </c>
       <c r="O2" t="n">
         <v>0.47</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>7</v>
+      </c>
+      <c r="U2" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.84</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43096</v>
+        <v>43097</v>
       </c>
       <c r="H3" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="I3" t="n">
         <v>102.7890115864769</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K3" t="n">
-        <v>10.22</v>
+        <v>8.44</v>
       </c>
       <c r="L3" t="n">
         <v>3.56</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>5</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>5.59</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43118</v>
+        <v>43119</v>
       </c>
       <c r="H4" t="n">
-        <v>102.5</v>
+        <v>101</v>
       </c>
       <c r="I4" t="n">
         <v>101.3781381672628</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.49</v>
+        <v>-1.94</v>
       </c>
       <c r="L4" t="n">
         <v>3.88</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.52</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43192</v>
+        <v>43193</v>
       </c>
       <c r="H5" t="n">
-        <v>86</v>
+        <v>87.5</v>
       </c>
       <c r="I5" t="n">
         <v>87.29023346346034</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K5" t="n">
-        <v>14.85</v>
+        <v>13.37</v>
       </c>
       <c r="L5" t="n">
         <v>1.98</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.93</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43293</v>
+        <v>43294</v>
       </c>
       <c r="H6" t="n">
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="I6" t="n">
         <v>92.77870756247421</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K6" t="n">
-        <v>9.710000000000001</v>
+        <v>5.71</v>
       </c>
       <c r="L6" t="n">
         <v>1.71</v>
       </c>
       <c r="M6" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>3.65</v>
       </c>
       <c r="O6" t="n">
         <v>1.74</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43357</v>
+        <v>43360</v>
       </c>
       <c r="H7" t="n">
-        <v>81</v>
+        <v>86.5</v>
       </c>
       <c r="I7" t="n">
         <v>84.82377500397315</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="K7" t="n">
-        <v>12.43</v>
+        <v>6.49</v>
       </c>
       <c r="L7" t="n">
         <v>3.78</v>
@@ -840,7 +923,7 @@
         <v>1.22</v>
       </c>
       <c r="N7" t="n">
-        <v>2.81</v>
+        <v>6.79</v>
       </c>
       <c r="O7" t="n">
         <v>-3.65</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.49</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>43368</v>
+        <v>43369</v>
       </c>
       <c r="H8" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I8" t="n">
         <v>79.46346802210357</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.51</v>
+        <v>-8.67</v>
       </c>
       <c r="L8" t="n">
         <v>8.67</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>43525</v>
+        <v>43529</v>
       </c>
       <c r="H9" t="n">
-        <v>63.5</v>
+        <v>67</v>
       </c>
       <c r="I9" t="n">
         <v>65.25242040799949</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="K9" t="n">
-        <v>19.62</v>
+        <v>15.19</v>
       </c>
       <c r="L9" t="n">
         <v>1.9</v>
@@ -954,7 +1061,7 @@
         <v>2.48</v>
       </c>
       <c r="N9" t="n">
-        <v>3.01</v>
+        <v>5.51</v>
       </c>
       <c r="O9" t="n">
         <v>-1.25</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>43370</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>9.359999999999999</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>43593</v>
+        <v>43594</v>
       </c>
       <c r="H10" t="n">
-        <v>68.5</v>
+        <v>68</v>
       </c>
       <c r="I10" t="n">
         <v>68.05778955044119</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K10" t="n">
-        <v>2.24</v>
+        <v>1.49</v>
       </c>
       <c r="L10" t="n">
         <v>5.22</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>43552</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>5.58</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>43619</v>
+        <v>43620</v>
       </c>
       <c r="H11" t="n">
-        <v>69</v>
+        <v>69.5</v>
       </c>
       <c r="I11" t="n">
         <v>69.45255578595443</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.47</v>
+        <v>-2.21</v>
       </c>
       <c r="L11" t="n">
-        <v>1.47</v>
+        <v>2.21</v>
       </c>
       <c r="M11" t="n">
         <v>3.05</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.44</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>43654</v>
+        <v>43655</v>
       </c>
       <c r="H12" t="n">
-        <v>66.5</v>
+        <v>66</v>
       </c>
       <c r="I12" t="n">
         <v>66.18613841291813</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.32</v>
+        <v>-5.04</v>
       </c>
       <c r="L12" t="n">
-        <v>5.04</v>
+        <v>5.76</v>
       </c>
       <c r="M12" t="n">
         <v>1.47</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>5.36</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>43700</v>
+        <v>43703</v>
       </c>
       <c r="H13" t="n">
-        <v>55</v>
+        <v>57.5</v>
       </c>
       <c r="I13" t="n">
         <v>55.11805462229752</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K13" t="n">
-        <v>16.67</v>
+        <v>12.88</v>
       </c>
       <c r="L13" t="n">
         <v>0.76</v>
       </c>
       <c r="M13" t="n">
-        <v>1.55</v>
+        <v>1.82</v>
       </c>
       <c r="N13" t="n">
         <v>5</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.77</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>43747</v>
+        <v>43748</v>
       </c>
       <c r="H14" t="n">
-        <v>59.5</v>
+        <v>57</v>
       </c>
       <c r="I14" t="n">
         <v>58.04251976888814</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K14" t="n">
-        <v>3.48</v>
+        <v>-0.87</v>
       </c>
       <c r="L14" t="n">
         <v>3.48</v>
@@ -1239,7 +1406,7 @@
         <v>0.85</v>
       </c>
       <c r="N14" t="n">
-        <v>3.42</v>
+        <v>4.2</v>
       </c>
       <c r="O14" t="n">
         <v>4.55</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>11.93</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43831</v>
+        <v>43832</v>
       </c>
       <c r="H15" t="n">
-        <v>55.5</v>
+        <v>58</v>
       </c>
       <c r="I15" t="n">
         <v>56.68007036663079</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K15" t="n">
-        <v>2.63</v>
+        <v>-1.75</v>
       </c>
       <c r="L15" t="n">
         <v>10.53</v>
@@ -1296,7 +1475,7 @@
         <v>1.82</v>
       </c>
       <c r="N15" t="n">
-        <v>3.42</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
         <v>-4.2</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>8.92</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43873</v>
+        <v>43874</v>
       </c>
       <c r="H16" t="n">
-        <v>60</v>
+        <v>57.5</v>
       </c>
       <c r="I16" t="n">
         <v>58.08344950436532</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K16" t="n">
-        <v>3.45</v>
+        <v>-0.86</v>
       </c>
       <c r="L16" t="n">
         <v>6.9</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>13.34</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43936</v>
+        <v>43937</v>
       </c>
       <c r="H17" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="I17" t="n">
         <v>39.25772769393608</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K17" t="n">
-        <v>34.78</v>
+        <v>30.43</v>
       </c>
       <c r="L17" t="n">
         <v>4.35</v>
@@ -1410,7 +1613,7 @@
         <v>3.03</v>
       </c>
       <c r="N17" t="n">
-        <v>6.35</v>
+        <v>6.67</v>
       </c>
       <c r="O17" t="n">
         <v>-4.17</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>20.01</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="H18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I18" t="n">
         <v>42.93932223811935</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L18" t="n">
         <v>7.5</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>20.15</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44004</v>
+        <v>44005</v>
       </c>
       <c r="H19" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I19" t="n">
         <v>48.39053722915938</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.9</v>
+        <v>-21.43</v>
       </c>
       <c r="L19" t="n">
-        <v>11.9</v>
+        <v>33.33</v>
       </c>
       <c r="M19" t="n">
-        <v>2.33</v>
+        <v>19.15</v>
       </c>
       <c r="N19" t="n">
-        <v>4.65</v>
+        <v>8.51</v>
       </c>
       <c r="O19" t="n">
         <v>-4.55</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.77</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="I20" t="n">
         <v>58.18727057174058</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K20" t="n">
-        <v>17.65</v>
+        <v>13.73</v>
       </c>
       <c r="L20" t="n">
         <v>4.9</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44007</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>16.43</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44149</v>
+        <v>44152</v>
       </c>
       <c r="H21" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I21" t="n">
         <v>58.80620644923694</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="L21" t="n">
         <v>6.9</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>11.39</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44221</v>
+        <v>44223</v>
       </c>
       <c r="H22" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="I22" t="n">
         <v>65.35000699159859</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K22" t="n">
-        <v>11.86</v>
+        <v>10.17</v>
       </c>
       <c r="L22" t="n">
         <v>3.39</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>9.4</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>44292</v>
+        <v>44293</v>
       </c>
       <c r="H23" t="n">
-        <v>65</v>
+        <v>67.5</v>
       </c>
       <c r="I23" t="n">
         <v>65.61089831755129</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="L23" t="n">
         <v>7.69</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>10.93</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>44417</v>
+        <v>44418</v>
       </c>
       <c r="H24" t="n">
-        <v>132.5</v>
+        <v>126.5</v>
       </c>
       <c r="I24" t="n">
         <v>127.2601372980892</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K24" t="n">
-        <v>96.3</v>
+        <v>87.41</v>
       </c>
       <c r="L24" t="n">
         <v>7.41</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>5</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>17.75</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>44447</v>
+        <v>44448</v>
       </c>
       <c r="H25" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I25" t="n">
         <v>136.2883183589245</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.35</v>
+        <v>-9.09</v>
       </c>
       <c r="L25" t="n">
-        <v>8.300000000000001</v>
+        <v>11.86</v>
       </c>
       <c r="M25" t="n">
         <v>0.8100000000000001</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>13.42</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>44550</v>
+        <v>44551</v>
       </c>
       <c r="H26" t="n">
-        <v>212.5</v>
+        <v>206.5</v>
       </c>
       <c r="I26" t="n">
         <v>209.3519166802459</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K26" t="n">
-        <v>53.99</v>
+        <v>49.64</v>
       </c>
       <c r="L26" t="n">
         <v>8.699999999999999</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>24.84</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>44580</v>
+        <v>44581</v>
       </c>
       <c r="H27" t="n">
-        <v>236</v>
+        <v>240.5</v>
       </c>
       <c r="I27" t="n">
         <v>238.9525589346577</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K27" t="n">
-        <v>-14.29</v>
+        <v>-16.46</v>
       </c>
       <c r="L27" t="n">
-        <v>15.5</v>
+        <v>17.68</v>
       </c>
       <c r="M27" t="n">
         <v>8.82</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>44560</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>12.09</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H28" t="n">
-        <v>231</v>
+        <v>208.5</v>
       </c>
       <c r="I28" t="n">
         <v>217.3887933537438</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.95</v>
+        <v>-13.31</v>
       </c>
       <c r="L28" t="n">
-        <v>13.72</v>
+        <v>14.14</v>
       </c>
       <c r="M28" t="n">
         <v>5.41</v>
       </c>
       <c r="N28" t="n">
-        <v>5.54</v>
+        <v>9.74</v>
       </c>
       <c r="O28" t="n">
         <v>1.91</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>22.47</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>44629</v>
+        <v>44630</v>
       </c>
       <c r="H29" t="n">
-        <v>245.5</v>
+        <v>291</v>
       </c>
       <c r="I29" t="n">
         <v>253.648144021293</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-17.75</v>
+        <v>-39.57</v>
       </c>
       <c r="L29" t="n">
-        <v>18.23</v>
+        <v>41.25</v>
       </c>
       <c r="M29" t="n">
-        <v>2.47</v>
+        <v>3.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.26</v>
+        <v>18.53</v>
       </c>
       <c r="O29" t="n">
         <v>-9.74</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>21.86</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H30" t="n">
-        <v>274.5</v>
+        <v>259</v>
       </c>
       <c r="I30" t="n">
         <v>270.4804982514959</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="K30" t="n">
-        <v>-5.67</v>
+        <v>-11</v>
       </c>
       <c r="L30" t="n">
         <v>13.57</v>
@@ -2151,7 +2510,7 @@
         <v>4.46</v>
       </c>
       <c r="N30" t="n">
-        <v>4.98</v>
+        <v>5.65</v>
       </c>
       <c r="O30" t="n">
         <v>18.53</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>18.42</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44771</v>
+        <v>44774</v>
       </c>
       <c r="H31" t="n">
-        <v>226</v>
+        <v>227.5</v>
       </c>
       <c r="I31" t="n">
         <v>227.4635325995618</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="K31" t="n">
-        <v>12.74</v>
+        <v>12.16</v>
       </c>
       <c r="L31" t="n">
         <v>5.98</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>8.34</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44826</v>
+        <v>44827</v>
       </c>
       <c r="H32" t="n">
-        <v>214.5</v>
+        <v>210.5</v>
       </c>
       <c r="I32" t="n">
         <v>213.454479244066</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K32" t="n">
-        <v>-5.71</v>
+        <v>-7.47</v>
       </c>
       <c r="L32" t="n">
         <v>8.57</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>9.33</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44988</v>
+        <v>44991</v>
       </c>
       <c r="H33" t="n">
-        <v>149.5</v>
+        <v>160.5</v>
       </c>
       <c r="I33" t="n">
         <v>158.1052382364793</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="K33" t="n">
-        <v>28.98</v>
+        <v>23.75</v>
       </c>
       <c r="L33" t="n">
         <v>2.61</v>
@@ -2322,7 +2717,7 @@
         <v>1.75</v>
       </c>
       <c r="N33" t="n">
-        <v>4.01</v>
+        <v>7.36</v>
       </c>
       <c r="O33" t="n">
         <v>-1.86</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>7</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>11.83</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45009</v>
+        <v>45012</v>
       </c>
       <c r="H34" t="n">
-        <v>142</v>
+        <v>137.5</v>
       </c>
       <c r="I34" t="n">
         <v>141.5108678737413</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.53</v>
+        <v>-14.33</v>
       </c>
       <c r="L34" t="n">
-        <v>12.46</v>
+        <v>14.95</v>
       </c>
       <c r="M34" t="n">
         <v>1.31</v>
       </c>
       <c r="N34" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="O34" t="n">
         <v>7.36</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>12.37</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45022</v>
+        <v>45026</v>
       </c>
       <c r="H35" t="n">
-        <v>150</v>
+        <v>152.5</v>
       </c>
       <c r="I35" t="n">
         <v>152.2080034017276</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.09</v>
+        <v>-10.91</v>
       </c>
       <c r="L35" t="n">
-        <v>10.91</v>
+        <v>11.27</v>
       </c>
       <c r="M35" t="n">
         <v>1.08</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.14</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45311</v>
+        <v>45314</v>
       </c>
       <c r="H36" t="n">
-        <v>747</v>
+        <v>704</v>
       </c>
       <c r="I36" t="n">
         <v>715.6307317606181</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="K36" t="n">
-        <v>389.84</v>
+        <v>361.64</v>
       </c>
       <c r="L36" t="n">
         <v>2.3</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>197</v>
+        <v>198</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>10</v>
+      </c>
+      <c r="U36" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>14.03</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45322</v>
+        <v>45323</v>
       </c>
       <c r="H37" t="n">
-        <v>774.5</v>
+        <v>831</v>
       </c>
       <c r="I37" t="n">
         <v>774.5115159256553</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-10.01</v>
+        <v>-18.04</v>
       </c>
       <c r="L37" t="n">
-        <v>10.94</v>
+        <v>18.75</v>
       </c>
       <c r="M37" t="n">
         <v>0.96</v>
       </c>
       <c r="N37" t="n">
-        <v>6.17</v>
+        <v>7.3</v>
       </c>
       <c r="O37" t="n">
         <v>-5.76</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>14.53</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45342</v>
+        <v>45343</v>
       </c>
       <c r="H38" t="n">
-        <v>765.5</v>
+        <v>738.5</v>
       </c>
       <c r="I38" t="n">
         <v>746.5391196934584</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K38" t="n">
-        <v>-7.88</v>
+        <v>-11.13</v>
       </c>
       <c r="L38" t="n">
-        <v>8.720000000000001</v>
+        <v>12.15</v>
       </c>
       <c r="M38" t="n">
         <v>2.63</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>14.72</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45373</v>
+        <v>45377</v>
       </c>
       <c r="H39" t="n">
-        <v>732.5</v>
+        <v>770</v>
       </c>
       <c r="I39" t="n">
         <v>765.5370677242471</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="K39" t="n">
-        <v>0.8100000000000001</v>
+        <v>-4.27</v>
       </c>
       <c r="L39" t="n">
         <v>9.210000000000001</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>16.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45420</v>
+        <v>45421</v>
       </c>
       <c r="H40" t="n">
-        <v>940</v>
+        <v>903.5</v>
       </c>
       <c r="I40" t="n">
         <v>910.797954176804</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K40" t="n">
-        <v>22.08</v>
+        <v>17.34</v>
       </c>
       <c r="L40" t="n">
         <v>4.09</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>3</v>
+      </c>
+      <c r="U40" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>19.6</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45503</v>
+        <v>45504</v>
       </c>
       <c r="H41" t="n">
-        <v>804</v>
+        <v>852</v>
       </c>
       <c r="I41" t="n">
         <v>825.9691948281993</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K41" t="n">
-        <v>11.01</v>
+        <v>5.7</v>
       </c>
       <c r="L41" t="n">
         <v>6.42</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>4</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>14.91</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45660</v>
+        <v>45663</v>
       </c>
       <c r="H42" t="n">
-        <v>1780</v>
+        <v>1696.5</v>
       </c>
       <c r="I42" t="n">
         <v>1702.306485618099</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K42" t="n">
-        <v>108.92</v>
+        <v>99.12</v>
       </c>
       <c r="L42" t="n">
         <v>9.800000000000001</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>6</v>
+      </c>
+      <c r="U42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>14.6</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45672</v>
+        <v>45673</v>
       </c>
       <c r="H43" t="n">
-        <v>1928.5</v>
+        <v>1998</v>
       </c>
       <c r="I43" t="n">
         <v>1930.651837222844</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K43" t="n">
-        <v>-13.68</v>
+        <v>-17.77</v>
       </c>
       <c r="L43" t="n">
-        <v>14.15</v>
+        <v>18.51</v>
       </c>
       <c r="M43" t="n">
         <v>2.3</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,22 +3455,22 @@
         <v>13.39</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45684</v>
+        <v>45685</v>
       </c>
       <c r="H44" t="n">
-        <v>1813.5</v>
+        <v>1719</v>
       </c>
       <c r="I44" t="n">
         <v>1775.260694138283</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K44" t="n">
-        <v>-9.23</v>
+        <v>-13.96</v>
       </c>
       <c r="L44" t="n">
-        <v>10.39</v>
+        <v>14.39</v>
       </c>
       <c r="M44" t="n">
         <v>2.16</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>18.51</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45707</v>
+        <v>45708</v>
       </c>
       <c r="H45" t="n">
-        <v>1877</v>
+        <v>1986.5</v>
       </c>
       <c r="I45" t="n">
         <v>1973.200711022866</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K45" t="n">
-        <v>-9.19</v>
+        <v>-15.56</v>
       </c>
       <c r="L45" t="n">
-        <v>13.58</v>
+        <v>16.03</v>
       </c>
       <c r="M45" t="n">
         <v>1.51</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>17.63</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45715</v>
+        <v>45716</v>
       </c>
       <c r="H46" t="n">
-        <v>1721</v>
+        <v>1544.5</v>
       </c>
       <c r="I46" t="n">
         <v>1660.904888497898</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K46" t="n">
-        <v>-13.37</v>
+        <v>-22.25</v>
       </c>
       <c r="L46" t="n">
-        <v>14.1</v>
+        <v>23.63</v>
       </c>
       <c r="M46" t="n">
         <v>1.88</v>
       </c>
       <c r="N46" t="n">
-        <v>6.16</v>
+        <v>10.26</v>
       </c>
       <c r="O46" t="n">
         <v>5.83</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>26.21</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45736</v>
+        <v>45737</v>
       </c>
       <c r="H47" t="n">
-        <v>1492.5</v>
+        <v>1593</v>
       </c>
       <c r="I47" t="n">
         <v>1577.503432976755</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K47" t="n">
-        <v>3.37</v>
+        <v>-3.14</v>
       </c>
       <c r="L47" t="n">
         <v>12.2</v>
@@ -3120,7 +3683,7 @@
         <v>1.88</v>
       </c>
       <c r="N47" t="n">
-        <v>5.93</v>
+        <v>6.73</v>
       </c>
       <c r="O47" t="n">
         <v>-10.26</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>19.53</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45820</v>
+        <v>45821</v>
       </c>
       <c r="H48" t="n">
-        <v>2754.1</v>
+        <v>2711.2</v>
       </c>
       <c r="I48" t="n">
         <v>2716.361883466463</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K48" t="n">
-        <v>72.89</v>
+        <v>70.19</v>
       </c>
       <c r="L48" t="n">
         <v>6.81</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>4</v>
+      </c>
+      <c r="U48" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>12.1</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="H49" t="n">
-        <v>2244.2</v>
+        <v>2330.2</v>
       </c>
       <c r="I49" t="n">
         <v>2253.715774658515</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K49" t="n">
-        <v>17.22</v>
+        <v>14.05</v>
       </c>
       <c r="L49" t="n">
         <v>5.69</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>11.59</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H50" t="n">
-        <v>2715.8</v>
+        <v>2581.7</v>
       </c>
       <c r="I50" t="n">
         <v>2687.173541128128</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K50" t="n">
-        <v>16.55</v>
+        <v>10.79</v>
       </c>
       <c r="L50" t="n">
         <v>4.3</v>
@@ -3291,7 +3890,7 @@
         <v>0.7</v>
       </c>
       <c r="N50" t="n">
-        <v>3.61</v>
+        <v>4.94</v>
       </c>
       <c r="O50" t="n">
         <v>3.83</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>3</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>13.71</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="H51" t="n">
-        <v>2832</v>
+        <v>2836.8</v>
       </c>
       <c r="I51" t="n">
         <v>2836.247191242083</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.880000000000001</v>
       </c>
       <c r="L51" t="n">
         <v>11.31</v>
@@ -3357,7 +3968,19 @@
         <v>1</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>8.74</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46052</v>
+        <v>46054</v>
       </c>
       <c r="H52" t="n">
-        <v>2797</v>
+        <v>2578.1</v>
       </c>
       <c r="I52" t="n">
         <v>2596.373561119377</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.4</v>
+        <v>-9.119999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>8.449999999999999</v>
+        <v>16.19</v>
       </c>
       <c r="M52" t="n">
         <v>0.55</v>
       </c>
       <c r="N52" t="n">
-        <v>2.92</v>
+        <v>7.83</v>
       </c>
       <c r="O52" t="n">
         <v>0.17</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>14.56</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H53" t="n">
-        <v>2897</v>
+        <v>2985.1</v>
       </c>
       <c r="I53" t="n">
         <v>2953.584719488404</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K53" t="n">
-        <v>-12.37</v>
+        <v>-15.79</v>
       </c>
       <c r="L53" t="n">
-        <v>13.62</v>
+        <v>16.28</v>
       </c>
       <c r="M53" t="n">
         <v>5.49</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>13.11</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46069</v>
+        <v>46070</v>
       </c>
       <c r="H54" t="n">
-        <v>2804.6</v>
+        <v>2742.3</v>
       </c>
       <c r="I54" t="n">
         <v>2804.599865380194</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K54" t="n">
-        <v>-6.05</v>
+        <v>-8.130000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M54" t="n">
         <v>7.12</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>15.36</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="H55" t="n">
-        <v>2862.6</v>
+        <v>2973.6</v>
       </c>
       <c r="I55" t="n">
         <v>2902.320271715246</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K55" t="n">
-        <v>-4.39</v>
+        <v>-8.43</v>
       </c>
       <c r="L55" t="n">
-        <v>5.65</v>
+        <v>8.67</v>
       </c>
       <c r="M55" t="n">
         <v>3.16</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>12.2</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="H56" t="n">
-        <v>2779.8</v>
+        <v>2683.5</v>
       </c>
       <c r="I56" t="n">
         <v>2686.337700754685</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K56" t="n">
-        <v>-6.52</v>
+        <v>-9.76</v>
       </c>
       <c r="L56" t="n">
-        <v>9.6</v>
+        <v>9.99</v>
       </c>
       <c r="M56" t="n">
         <v>1.52</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>13.02</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="H57" t="n">
-        <v>2950.8</v>
+        <v>3163.6</v>
       </c>
       <c r="I57" t="n">
         <v>3033.009114750907</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K57" t="n">
-        <v>-9.960000000000001</v>
+        <v>-17.89</v>
       </c>
       <c r="L57" t="n">
-        <v>11.79</v>
+        <v>19.57</v>
       </c>
       <c r="M57" t="n">
         <v>4.73</v>
       </c>
       <c r="N57" t="n">
-        <v>6.86</v>
+        <v>7.21</v>
       </c>
       <c r="O57" t="n">
         <v>-3.46</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>13.8</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="H58" t="n">
-        <v>4066.6</v>
+        <v>3931.9</v>
       </c>
       <c r="I58" t="n">
         <v>3998.225125397088</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K58" t="n">
-        <v>28.54</v>
+        <v>24.29</v>
       </c>
       <c r="L58" t="n">
         <v>4.17</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>11.32</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H59" t="n">
-        <v>3338</v>
+        <v>3428</v>
       </c>
       <c r="I59" t="n">
         <v>3399.580828704293</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K59" t="n">
-        <v>15.1</v>
+        <v>12.82</v>
       </c>
       <c r="L59" t="n">
         <v>7.32</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3864,6 +4583,14 @@
       <c r="Q60" t="n">
         <v>9</v>
       </c>
+      <c r="R60" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7972,7 +8699,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59.2</v>
+        <v>60.8</v>
       </c>
     </row>
     <row r="6">
@@ -7982,7 +8709,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="7">
@@ -7992,7 +8719,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8">
@@ -8002,7 +8729,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9">
@@ -8012,7 +8739,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>81.8</v>
+        <v>83.8</v>
       </c>
     </row>
     <row r="10">
@@ -8022,7 +8749,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135.5</v>
+        <v>136.5</v>
       </c>
     </row>
     <row r="11">
@@ -8032,7 +8759,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -8042,7 +8769,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -8052,7 +8779,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39.7</v>
+        <v>37.9</v>
       </c>
     </row>
     <row r="14">
@@ -8062,7 +8789,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.56</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="15">
@@ -8072,7 +8799,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>26.63</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="16">
@@ -8082,7 +8809,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.49</v>
+        <v>-2.15</v>
       </c>
     </row>
     <row r="17">
@@ -8092,7 +8819,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>389.84</v>
+        <v>361.64</v>
       </c>
     </row>
     <row r="18">
@@ -8102,7 +8829,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>51.7</v>
+        <v>43.1</v>
       </c>
     </row>
     <row r="19">
@@ -8112,7 +8839,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>7.81</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="20">
@@ -8122,7 +8849,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>7.6</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
     <row r="21">
@@ -8132,7 +8859,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.23</v>
+        <v>41.25</v>
       </c>
     </row>
     <row r="22">
@@ -8152,7 +8879,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -8162,7 +8889,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.92</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="25">
@@ -8172,7 +8899,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>15</v>
+        <v>19.15</v>
       </c>
     </row>
     <row r="26">
@@ -8182,7 +8909,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.21</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="27">
@@ -8192,7 +8919,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.64</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="28">
@@ -8202,7 +8929,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
